--- a/Employee_Reports_wi52/Alvin Cataquiz Austria Q0547.xlsx
+++ b/Employee_Reports_wi52/Alvin Cataquiz Austria Q0547.xlsx
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>608</v>
+        <v>600</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>609</v>
+        <v>601</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>610</v>
+        <v>602</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>610</v>
+        <v>602</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -774,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>611</v>
+        <v>603</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -823,11 +823,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>611</v>
+        <v>603</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -872,11 +872,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>614</v>
+        <v>606</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -921,11 +921,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>614</v>
+        <v>606</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -970,11 +970,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>615</v>
+        <v>607</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1019,11 +1019,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>615</v>
+        <v>607</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1068,11 +1068,11 @@
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-2</v>
+        <v>-10</v>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -1117,11 +1117,11 @@
         </is>
       </c>
       <c r="H14" s="5" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
@@ -1166,11 +1166,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>615</v>
+        <v>607</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1215,11 +1215,11 @@
         </is>
       </c>
       <c r="H16" s="5" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
@@ -1264,11 +1264,11 @@
         </is>
       </c>
       <c r="H17" s="5" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
@@ -1314,11 +1314,11 @@
         </is>
       </c>
       <c r="H18" s="5" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
@@ -1363,11 +1363,11 @@
         </is>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-443</v>
+        <v>-451</v>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -1412,11 +1412,11 @@
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-371</v>
+        <v>-379</v>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -1461,11 +1461,11 @@
         </is>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-167</v>
+        <v>-175</v>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -1510,11 +1510,11 @@
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-182</v>
+        <v>-190</v>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -1559,11 +1559,11 @@
         </is>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-156</v>
+        <v>-164</v>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -1587,20 +1587,20 @@
       <c r="E24" s="3" t="inlineStr"/>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>01-Jul-2025</t>
+          <t>24-Aug-2026</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>01-Jul-2027</t>
+          <t>23-Aug-2028</t>
         </is>
       </c>
       <c r="H24" s="3" t="n">
-        <v>315</v>
+        <v>726</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -1633,11 +1633,11 @@
         </is>
       </c>
       <c r="H25" s="3" t="n">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -2056,7 +2056,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7907</v>
+        <v>7899</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7902</v>
+        <v>7894</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7902</v>
+        <v>7894</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7899</v>
+        <v>7891</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7899</v>
+        <v>7891</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>7899</v>
+        <v>7891</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>7923</v>
+        <v>7915</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -2325,7 +2325,7 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>7923</v>
+        <v>7915</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>7902</v>
+        <v>7894</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>7923</v>
+        <v>7915</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -2412,7 +2412,7 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>7969</v>
+        <v>7961</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>7969</v>
+        <v>7961</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>7969</v>
+        <v>7961</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>7969</v>
+        <v>7961</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -2528,7 +2528,7 @@
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>7969</v>
+        <v>7961</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>7923</v>
+        <v>7915</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -2586,7 +2586,7 @@
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>7923</v>
+        <v>7915</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>7975</v>
+        <v>7967</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -2644,7 +2644,7 @@
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>7975</v>
+        <v>7967</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>7975</v>
+        <v>7967</v>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
@@ -2702,7 +2702,7 @@
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>7975</v>
+        <v>7967</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>7975</v>
+        <v>7967</v>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
